--- a/output/laminas_provinciales/prov_i_ingr_median_a_2023_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2023_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:12</t>
+    <t xml:space="preserve">2026-09-09 22:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2023_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2023_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:09</t>
+    <t xml:space="preserve">2026-09-17 13:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>987680</v>
+        <v>950210</v>
       </c>
     </row>
     <row r="3">
@@ -1115,26 +1115,26 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>821202.5</v>
+        <v>987680</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>750000</v>
+        <v>821202.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>950210</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="7">
@@ -1175,35 +1175,35 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>885384</v>
+        <v>849170</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>987680</v>
+        <v>950210</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1058965</v>
+        <v>1019170</v>
       </c>
     </row>
     <row r="5">
@@ -1241,101 +1241,101 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>732934</v>
+        <v>885384</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>821202.5</v>
+        <v>987680</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>873983</v>
+        <v>1058965</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>656879.5</v>
+        <v>732934</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>750000</v>
+        <v>821202.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>803940</v>
+        <v>873983</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>849170</v>
+        <v>656879.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>950210</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1019170</v>
+        <v>803940</v>
       </c>
     </row>
     <row r="17">

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2023_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2023_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:39</t>
+    <t xml:space="preserve">2026-09-25 21:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2023_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2023_metropolitana.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:38</t>
+    <t xml:space="preserve">2026-10-05 07:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -577,7 +577,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>821202</v>
+        <v>821203</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>732934</v>
@@ -756,7 +756,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>801688</v>
+        <v>801689</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>920102</v>
